--- a/plots/countries/sectors/Thailand-sectors.xlsx
+++ b/plots/countries/sectors/Thailand-sectors.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">Author</t>
   </si>
@@ -30,13 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2025). Tidy GHG Inventories (1.0) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14945466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See also</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
@@ -443,14 +437,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -464,39 +450,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>1990</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -504,19 +490,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>1990</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -524,19 +510,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>1990</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -544,19 +530,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>1990</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>14.1966523751164</v>
@@ -564,19 +550,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>1990</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -584,19 +570,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>1990</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -604,19 +590,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>1990</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -624,19 +610,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>1990</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -644,19 +630,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>1990</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -664,19 +650,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
       <c r="D11" t="n">
         <v>2000</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>50.0991371221983</v>
@@ -684,19 +670,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>2000</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
         <v>70.83086238357</v>
@@ -704,19 +690,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
         <v>2000</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>7.79229124769947</v>
@@ -724,19 +710,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
         <v>2000</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
         <v>60.91441145352</v>
@@ -744,19 +730,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>2000</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
         <v>58.3665404791302</v>
@@ -764,19 +750,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>2000</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
         <v>0.0380480757888</v>
@@ -784,19 +770,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>2000</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
         <v>21.207119599284</v>
@@ -804,19 +790,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
         <v>2000</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>-100.9787497944</v>
@@ -824,19 +810,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
         <v>2000</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
         <v>7.71739788547542</v>
@@ -844,19 +830,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>2001</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
         <v>51.0614222832179</v>
@@ -864,19 +850,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
         <v>2001</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>71.74297671894</v>
@@ -884,19 +870,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
         <v>2001</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>7.56591660649097</v>
@@ -904,19 +890,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
         <v>2001</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
         <v>50.21720698869</v>
@@ -924,19 +910,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>2001</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
         <v>61.7940270791262</v>
@@ -944,19 +930,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
         <v>2001</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>0.040052715456</v>
@@ -964,19 +950,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>2001</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
         <v>22.7868369511593</v>
@@ -984,19 +970,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>2001</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
         <v>-105.076484695632</v>
@@ -1004,19 +990,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
         <v>2001</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
         <v>8.14972178525372</v>
@@ -1024,19 +1010,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
       </c>
       <c r="D29" t="n">
         <v>2002</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
         <v>49.4457592020335</v>
@@ -1044,19 +1030,19 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
         <v>2002</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
         <v>73.22244197089</v>
@@ -1064,19 +1050,19 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
         <v>2002</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>7.88794958599816</v>
@@ -1084,19 +1070,19 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D32" t="n">
         <v>2002</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
         <v>57.36349014494</v>
@@ -1104,19 +1090,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" t="n">
         <v>2002</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
         <v>64.1179444409952</v>
@@ -1124,19 +1110,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
         <v>2002</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
         <v>0.0442220343264</v>
@@ -1144,19 +1130,19 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
         <v>2002</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
         <v>24.8506974939185</v>
@@ -1164,19 +1150,19 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D36" t="n">
         <v>2002</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
         <v>-106.3527823454</v>
@@ -1184,19 +1170,19 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
         <v>2002</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
         <v>9.42517962585713</v>
@@ -1204,19 +1190,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
         <v>14</v>
-      </c>
-      <c r="B38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" t="s">
-        <v>16</v>
       </c>
       <c r="D38" t="n">
         <v>2003</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
         <v>53.5408141685237</v>
@@ -1224,19 +1210,19 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
         <v>2003</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
         <v>74.52909711497</v>
@@ -1244,19 +1230,19 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D40" t="n">
         <v>2003</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
         <v>7.75148833063558</v>
@@ -1264,19 +1250,19 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D41" t="n">
         <v>2003</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
         <v>66.190850827225</v>
@@ -1284,19 +1270,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D42" t="n">
         <v>2003</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
         <v>66.845710393446</v>
@@ -1304,19 +1290,19 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D43" t="n">
         <v>2003</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
         <v>0.0433758380256</v>
@@ -1324,19 +1310,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
         <v>2003</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
         <v>24.0745674029226</v>
@@ -1344,19 +1330,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D45" t="n">
         <v>2003</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F45" t="n">
         <v>-107.856943033297</v>
@@ -1364,19 +1350,19 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D46" t="n">
         <v>2003</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
         <v>10.6531558454825</v>
@@ -1384,19 +1370,19 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
         <v>14</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" t="s">
-        <v>16</v>
       </c>
       <c r="D47" t="n">
         <v>2004</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
         <v>53.2328866196872</v>
@@ -1404,19 +1390,19 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D48" t="n">
         <v>2004</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
         <v>82.09891812942</v>
@@ -1424,19 +1410,19 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
         <v>2004</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
         <v>8.53061069803702</v>
@@ -1444,19 +1430,19 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D50" t="n">
         <v>2004</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F50" t="n">
         <v>69.70512852664</v>
@@ -1464,19 +1450,19 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
         <v>2004</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F51" t="n">
         <v>72.3823164741122</v>
@@ -1484,19 +1470,19 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D52" t="n">
         <v>2004</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F52" t="n">
         <v>0.0369228978912</v>
@@ -1504,19 +1490,19 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D53" t="n">
         <v>2004</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
         <v>25.8174647400885</v>
@@ -1524,19 +1510,19 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D54" t="n">
         <v>2004</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
         <v>-109.798081828448</v>
@@ -1544,19 +1530,19 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D55" t="n">
         <v>2004</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
         <v>10.9425918845234</v>
@@ -1564,19 +1550,19 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
         <v>14</v>
-      </c>
-      <c r="B56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" t="s">
-        <v>16</v>
       </c>
       <c r="D56" t="n">
         <v>2005</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>52.1279878305157</v>
@@ -1584,19 +1570,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
         <v>2005</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F57" t="n">
         <v>79.08949977571</v>
@@ -1604,19 +1590,19 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D58" t="n">
         <v>2005</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
         <v>9.00831135057218</v>
@@ -1624,19 +1610,19 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D59" t="n">
         <v>2005</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F59" t="n">
         <v>77.04108484826</v>
@@ -1644,19 +1630,19 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D60" t="n">
         <v>2005</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
         <v>75.755046624823</v>
@@ -1664,19 +1650,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D61" t="n">
         <v>2005</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
         <v>0.0366854497344</v>
@@ -1684,19 +1670,19 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D62" t="n">
         <v>2005</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
         <v>27.6853821457198</v>
@@ -1704,19 +1690,19 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D63" t="n">
         <v>2005</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
         <v>-112.44177119787</v>
@@ -1724,19 +1710,19 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D64" t="n">
         <v>2005</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F64" t="n">
         <v>10.9419704170576</v>
@@ -1744,19 +1730,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
         <v>14</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" t="s">
-        <v>16</v>
       </c>
       <c r="D65" t="n">
         <v>2006</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F65" t="n">
         <v>54.4812361558592</v>
@@ -1764,19 +1750,19 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D66" t="n">
         <v>2006</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
         <v>83.76419448106</v>
@@ -1784,19 +1770,19 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D67" t="n">
         <v>2006</v>
       </c>
       <c r="E67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
         <v>9.16821526770644</v>
@@ -1804,19 +1790,19 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D68" t="n">
         <v>2006</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
         <v>76.432363333245</v>
@@ -1824,19 +1810,19 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
         <v>2006</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
         <v>75.8220959200059</v>
@@ -1844,19 +1830,19 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D70" t="n">
         <v>2006</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
         <v>0.0379045521024</v>
@@ -1864,19 +1850,19 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
         <v>2006</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
         <v>28.5624047221323</v>
@@ -1884,19 +1870,19 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D72" t="n">
         <v>2006</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
         <v>-115.981166413061</v>
@@ -1904,19 +1890,19 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D73" t="n">
         <v>2006</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
         <v>11.7929139822623</v>
@@ -1924,19 +1910,19 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
         <v>14</v>
-      </c>
-      <c r="B74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" t="s">
-        <v>16</v>
       </c>
       <c r="D74" t="n">
         <v>2007</v>
       </c>
       <c r="E74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F74" t="n">
         <v>57.8265119912688</v>
@@ -1944,19 +1930,19 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D75" t="n">
         <v>2007</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
         <v>82.94017460439</v>
@@ -1964,19 +1950,19 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D76" t="n">
         <v>2007</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F76" t="n">
         <v>9.69520230998295</v>
@@ -1984,19 +1970,19 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D77" t="n">
         <v>2007</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
         <v>82.206229006265</v>
@@ -2004,19 +1990,19 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
         <v>2007</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
         <v>82.1116785819183</v>
@@ -2024,19 +2010,19 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D79" t="n">
         <v>2007</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
         <v>0.0367936675104</v>
@@ -2044,19 +2030,19 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D80" t="n">
         <v>2007</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F80" t="n">
         <v>30.2020964011318</v>
@@ -2064,19 +2050,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D81" t="n">
         <v>2007</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F81" t="n">
         <v>-119.616472725946</v>
@@ -2084,19 +2070,19 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D82" t="n">
         <v>2007</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>12.1070819487194</v>
@@ -2104,19 +2090,19 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
         <v>14</v>
-      </c>
-      <c r="B83" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" t="s">
-        <v>16</v>
       </c>
       <c r="D83" t="n">
         <v>2008</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F83" t="n">
         <v>59.5549547955744</v>
@@ -2124,19 +2110,19 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D84" t="n">
         <v>2008</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F84" t="n">
         <v>86.2508003731365</v>
@@ -2144,19 +2130,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D85" t="n">
         <v>2008</v>
       </c>
       <c r="E85" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F85" t="n">
         <v>10.1945183716107</v>
@@ -2164,19 +2150,19 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D86" t="n">
         <v>2008</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
         <v>88.1095763868606</v>
@@ -2184,19 +2170,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D87" t="n">
         <v>2008</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F87" t="n">
         <v>83.3650686271616</v>
@@ -2204,19 +2190,19 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D88" t="n">
         <v>2008</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F88" t="n">
         <v>0.05260973302164</v>
@@ -2224,19 +2210,19 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D89" t="n">
         <v>2008</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F89" t="n">
         <v>28.6632441934283</v>
@@ -2244,19 +2230,19 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D90" t="n">
         <v>2008</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F90" t="n">
         <v>-122.714589648647</v>
@@ -2264,19 +2250,19 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D91" t="n">
         <v>2008</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F91" t="n">
         <v>13.1412647595872</v>
@@ -2284,19 +2270,19 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
         <v>14</v>
-      </c>
-      <c r="B92" t="s">
-        <v>15</v>
-      </c>
-      <c r="C92" t="s">
-        <v>16</v>
       </c>
       <c r="D92" t="n">
         <v>2009</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
         <v>61.635730509684</v>
@@ -2304,19 +2290,19 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D93" t="n">
         <v>2009</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F93" t="n">
         <v>84.7531703434601</v>
@@ -2324,19 +2310,19 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D94" t="n">
         <v>2009</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
         <v>9.78864916411182</v>
@@ -2344,19 +2330,19 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D95" t="n">
         <v>2009</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
         <v>92.4401643646797</v>
@@ -2364,19 +2350,19 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D96" t="n">
         <v>2009</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
         <v>81.8333928968428</v>
@@ -2384,19 +2370,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D97" t="n">
         <v>2009</v>
       </c>
       <c r="E97" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
         <v>0.0501108485748</v>
@@ -2404,19 +2390,19 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D98" t="n">
         <v>2009</v>
       </c>
       <c r="E98" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F98" t="n">
         <v>28.0859157967555</v>
@@ -2424,19 +2410,19 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D99" t="n">
         <v>2009</v>
       </c>
       <c r="E99" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F99" t="n">
         <v>-125.275561293074</v>
@@ -2444,19 +2430,19 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D100" t="n">
         <v>2009</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F100" t="n">
         <v>12.8017002873093</v>
@@ -2464,19 +2450,19 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" t="s">
         <v>14</v>
-      </c>
-      <c r="B101" t="s">
-        <v>15</v>
-      </c>
-      <c r="C101" t="s">
-        <v>16</v>
       </c>
       <c r="D101" t="n">
         <v>2010</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F101" t="n">
         <v>62.6169127624594</v>
@@ -2484,19 +2470,19 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D102" t="n">
         <v>2010</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F102" t="n">
         <v>95.0493827383329</v>
@@ -2504,19 +2490,19 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D103" t="n">
         <v>2010</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F103" t="n">
         <v>10.9220055275473</v>
@@ -2524,19 +2510,19 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D104" t="n">
         <v>2010</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
         <v>84.8812846916627</v>
@@ -2544,19 +2530,19 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D105" t="n">
         <v>2010</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F105" t="n">
         <v>87.8856011426087</v>
@@ -2564,19 +2550,19 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D106" t="n">
         <v>2010</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F106" t="n">
         <v>0.05414802474762</v>
@@ -2584,19 +2570,19 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D107" t="n">
         <v>2010</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F107" t="n">
         <v>29.7000165923405</v>
@@ -2604,19 +2590,19 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D108" t="n">
         <v>2010</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F108" t="n">
         <v>-128.238277286573</v>
@@ -2624,19 +2610,19 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D109" t="n">
         <v>2010</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F109" t="n">
         <v>11.1390267425878</v>
@@ -2644,19 +2630,19 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
         <v>14</v>
-      </c>
-      <c r="B110" t="s">
-        <v>15</v>
-      </c>
-      <c r="C110" t="s">
-        <v>16</v>
       </c>
       <c r="D110" t="n">
         <v>2011</v>
       </c>
       <c r="E110" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F110" t="n">
         <v>62.7060582590366</v>
@@ -2664,19 +2650,19 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D111" t="n">
         <v>2011</v>
       </c>
       <c r="E111" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F111" t="n">
         <v>91.7626872124403</v>
@@ -2684,19 +2670,19 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D112" t="n">
         <v>2011</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F112" t="n">
         <v>11.213141185644</v>
@@ -2704,19 +2690,19 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D113" t="n">
         <v>2011</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F113" t="n">
         <v>92.8629263844121</v>
@@ -2724,19 +2710,19 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D114" t="n">
         <v>2011</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F114" t="n">
         <v>87.0164522022234</v>
@@ -2744,19 +2730,19 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D115" t="n">
         <v>2011</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F115" t="n">
         <v>0.066810253947705</v>
@@ -2764,19 +2750,19 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D116" t="n">
         <v>2011</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F116" t="n">
         <v>31.0103956244015</v>
@@ -2784,19 +2770,19 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D117" t="n">
         <v>2011</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F117" t="n">
         <v>-132.882133419423</v>
@@ -2804,19 +2790,19 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D118" t="n">
         <v>2011</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F118" t="n">
         <v>9.77266415844263</v>
@@ -2824,19 +2810,19 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" t="s">
         <v>14</v>
-      </c>
-      <c r="B119" t="s">
-        <v>15</v>
-      </c>
-      <c r="C119" t="s">
-        <v>16</v>
       </c>
       <c r="D119" t="n">
         <v>2012</v>
       </c>
       <c r="E119" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F119" t="n">
         <v>65.778120459839</v>
@@ -2844,19 +2830,19 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D120" t="n">
         <v>2012</v>
       </c>
       <c r="E120" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F120" t="n">
         <v>71.6338216831144</v>
@@ -2864,19 +2850,19 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D121" t="n">
         <v>2012</v>
       </c>
       <c r="E121" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F121" t="n">
         <v>13.0665749146269</v>
@@ -2884,19 +2870,19 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D122" t="n">
         <v>2012</v>
       </c>
       <c r="E122" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F122" t="n">
         <v>110.39839877948</v>
@@ -2904,19 +2890,19 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D123" t="n">
         <v>2012</v>
       </c>
       <c r="E123" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F123" t="n">
         <v>91.1821889061215</v>
@@ -2924,19 +2910,19 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D124" t="n">
         <v>2012</v>
       </c>
       <c r="E124" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F124" t="n">
         <v>0.0755428848438</v>
@@ -2944,19 +2930,19 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D125" t="n">
         <v>2012</v>
       </c>
       <c r="E125" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F125" t="n">
         <v>33.131913112</v>
@@ -2964,19 +2950,19 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D126" t="n">
         <v>2012</v>
       </c>
       <c r="E126" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F126" t="n">
         <v>-141.299645713866</v>
@@ -2984,19 +2970,19 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D127" t="n">
         <v>2012</v>
       </c>
       <c r="E127" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F127" t="n">
         <v>6.10661464681762</v>
@@ -3004,19 +2990,19 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>12</v>
+      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" t="s">
         <v>14</v>
-      </c>
-      <c r="B128" t="s">
-        <v>15</v>
-      </c>
-      <c r="C128" t="s">
-        <v>16</v>
       </c>
       <c r="D128" t="n">
         <v>2013</v>
       </c>
       <c r="E128" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F128" t="n">
         <v>61.2151018814629</v>
@@ -3024,19 +3010,19 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D129" t="n">
         <v>2013</v>
       </c>
       <c r="E129" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F129" t="n">
         <v>75.71750633731</v>
@@ -3044,19 +3030,19 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D130" t="n">
         <v>2013</v>
       </c>
       <c r="E130" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F130" t="n">
         <v>13.2378735013614</v>
@@ -3064,19 +3050,19 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D131" t="n">
         <v>2013</v>
       </c>
       <c r="E131" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F131" t="n">
         <v>106.274557336108</v>
@@ -3084,19 +3070,19 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D132" t="n">
         <v>2013</v>
       </c>
       <c r="E132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F132" t="n">
         <v>88.6423410818569</v>
@@ -3104,19 +3090,19 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C133" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D133" t="n">
         <v>2013</v>
       </c>
       <c r="E133" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F133" t="n">
         <v>0.0897864491784001</v>
@@ -3124,19 +3110,19 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D134" t="n">
         <v>2013</v>
       </c>
       <c r="E134" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F134" t="n">
         <v>32.9363560365896</v>
@@ -3144,19 +3130,19 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D135" t="n">
         <v>2013</v>
       </c>
       <c r="E135" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F135" t="n">
         <v>-144.732646535008</v>
@@ -3164,19 +3150,19 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D136" t="n">
         <v>2013</v>
       </c>
       <c r="E136" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F136" t="n">
         <v>7.97189825953038</v>
@@ -3184,19 +3170,19 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" t="s">
         <v>14</v>
-      </c>
-      <c r="B137" t="s">
-        <v>15</v>
-      </c>
-      <c r="C137" t="s">
-        <v>16</v>
       </c>
       <c r="D137" t="n">
         <v>2014</v>
       </c>
       <c r="E137" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F137" t="n">
         <v>60.0538901372774</v>
@@ -3204,19 +3190,19 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D138" t="n">
         <v>2014</v>
       </c>
       <c r="E138" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F138" t="n">
         <v>89.6199363840908</v>
@@ -3224,19 +3210,19 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C139" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D139" t="n">
         <v>2014</v>
       </c>
       <c r="E139" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F139" t="n">
         <v>13.2469382385445</v>
@@ -3244,19 +3230,19 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D140" t="n">
         <v>2014</v>
       </c>
       <c r="E140" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F140" t="n">
         <v>117.093684638285</v>
@@ -3264,19 +3250,19 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D141" t="n">
         <v>2014</v>
       </c>
       <c r="E141" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F141" t="n">
         <v>93.6041928118369</v>
@@ -3284,19 +3270,19 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D142" t="n">
         <v>2014</v>
       </c>
       <c r="E142" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F142" t="n">
         <v>0.0903308521258614</v>
@@ -3304,19 +3290,19 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D143" t="n">
         <v>2014</v>
       </c>
       <c r="E143" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F143" t="n">
         <v>34.4472011062749</v>
@@ -3324,19 +3310,19 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D144" t="n">
         <v>2014</v>
       </c>
       <c r="E144" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F144" t="n">
         <v>-147.487488050596</v>
@@ -3344,19 +3330,19 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C145" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D145" t="n">
         <v>2014</v>
       </c>
       <c r="E145" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F145" t="n">
         <v>7.50460523024922</v>
@@ -3364,19 +3350,19 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" t="s">
         <v>14</v>
-      </c>
-      <c r="B146" t="s">
-        <v>15</v>
-      </c>
-      <c r="C146" t="s">
-        <v>16</v>
       </c>
       <c r="D146" t="n">
         <v>2015</v>
       </c>
       <c r="E146" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F146" t="n">
         <v>53.2389628004979</v>
@@ -3384,19 +3370,19 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D147" t="n">
         <v>2015</v>
       </c>
       <c r="E147" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F147" t="n">
         <v>93.1826240588404</v>
@@ -3404,19 +3390,19 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C148" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D148" t="n">
         <v>2015</v>
       </c>
       <c r="E148" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F148" t="n">
         <v>12.1319503812017</v>
@@ -3424,19 +3410,19 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D149" t="n">
         <v>2015</v>
       </c>
       <c r="E149" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F149" t="n">
         <v>104.993162819452</v>
@@ -3444,19 +3430,19 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C150" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D150" t="n">
         <v>2015</v>
       </c>
       <c r="E150" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F150" t="n">
         <v>91.7133825412565</v>
@@ -3464,19 +3450,19 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C151" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D151" t="n">
         <v>2015</v>
       </c>
       <c r="E151" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F151" t="n">
         <v>0.092876579366784</v>
@@ -3484,19 +3470,19 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C152" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D152" t="n">
         <v>2015</v>
       </c>
       <c r="E152" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F152" t="n">
         <v>35.2427032100486</v>
@@ -3504,19 +3490,19 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C153" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D153" t="n">
         <v>2015</v>
       </c>
       <c r="E153" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F153" t="n">
         <v>-145.57795787285</v>
@@ -3524,19 +3510,19 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D154" t="n">
         <v>2015</v>
       </c>
       <c r="E154" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F154" t="n">
         <v>8.73538209883547</v>
@@ -3544,19 +3530,19 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
+        <v>12</v>
+      </c>
+      <c r="B155" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155" t="s">
         <v>14</v>
-      </c>
-      <c r="B155" t="s">
-        <v>15</v>
-      </c>
-      <c r="C155" t="s">
-        <v>16</v>
       </c>
       <c r="D155" t="n">
         <v>2016</v>
       </c>
       <c r="E155" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F155" t="n">
         <v>52.9171118063682</v>
@@ -3564,19 +3550,19 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D156" t="n">
         <v>2016</v>
       </c>
       <c r="E156" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F156" t="n">
         <v>79.703583636703</v>
@@ -3584,19 +3570,19 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C157" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D157" t="n">
         <v>2016</v>
       </c>
       <c r="E157" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F157" t="n">
         <v>12.1679717285282</v>
@@ -3604,19 +3590,19 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C158" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D158" t="n">
         <v>2016</v>
       </c>
       <c r="E158" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F158" t="n">
         <v>90.5860535828296</v>
@@ -3624,19 +3610,19 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C159" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D159" t="n">
         <v>2016</v>
       </c>
       <c r="E159" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F159" t="n">
         <v>97.9744480448985</v>
@@ -3644,19 +3630,19 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D160" t="n">
         <v>2016</v>
       </c>
       <c r="E160" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F160" t="n">
         <v>0.0766050166902152</v>
@@ -3664,19 +3650,19 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C161" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D161" t="n">
         <v>2016</v>
       </c>
       <c r="E161" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F161" t="n">
         <v>36.6731168530581</v>
@@ -3684,19 +3670,19 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C162" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D162" t="n">
         <v>2016</v>
       </c>
       <c r="E162" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F162" t="n">
         <v>-144.5588187752</v>
@@ -3704,19 +3690,19 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D163" t="n">
         <v>2016</v>
       </c>
       <c r="E163" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F163" t="n">
         <v>9.32518985805594</v>
@@ -3724,19 +3710,19 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>12</v>
+      </c>
+      <c r="B164" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" t="s">
         <v>14</v>
-      </c>
-      <c r="B164" t="s">
-        <v>15</v>
-      </c>
-      <c r="C164" t="s">
-        <v>16</v>
       </c>
       <c r="D164" t="n">
         <v>2017</v>
       </c>
       <c r="E164" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F164" t="n">
         <v>58.0827204808559</v>
@@ -3744,19 +3730,19 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C165" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D165" t="n">
         <v>2017</v>
       </c>
       <c r="E165" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F165" t="n">
         <v>77.7054944398201</v>
@@ -3764,19 +3750,19 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C166" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D166" t="n">
         <v>2017</v>
       </c>
       <c r="E166" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F166" t="n">
         <v>11.8816968000191</v>
@@ -3784,19 +3770,19 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C167" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D167" t="n">
         <v>2017</v>
       </c>
       <c r="E167" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F167" t="n">
         <v>98.0116262749786</v>
@@ -3804,19 +3790,19 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C168" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D168" t="n">
         <v>2017</v>
       </c>
       <c r="E168" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F168" t="n">
         <v>97.7673069500281</v>
@@ -3824,19 +3810,19 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C169" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D169" t="n">
         <v>2017</v>
       </c>
       <c r="E169" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F169" t="n">
         <v>0.108148395600877</v>
@@ -3844,19 +3830,19 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C170" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D170" t="n">
         <v>2017</v>
       </c>
       <c r="E170" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F170" t="n">
         <v>37.5324858678154</v>
@@ -3864,19 +3850,19 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C171" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D171" t="n">
         <v>2017</v>
       </c>
       <c r="E171" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F171" t="n">
         <v>-144.378924164978</v>
@@ -3884,19 +3870,19 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C172" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D172" t="n">
         <v>2017</v>
       </c>
       <c r="E172" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F172" t="n">
         <v>9.97862426070812</v>
@@ -3904,19 +3890,19 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
+        <v>12</v>
+      </c>
+      <c r="B173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" t="s">
         <v>14</v>
-      </c>
-      <c r="B173" t="s">
-        <v>15</v>
-      </c>
-      <c r="C173" t="s">
-        <v>16</v>
       </c>
       <c r="D173" t="n">
         <v>2018</v>
       </c>
       <c r="E173" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F173" t="n">
         <v>59.1193751059913</v>
@@ -3924,19 +3910,19 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D174" t="n">
         <v>2018</v>
       </c>
       <c r="E174" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F174" t="n">
         <v>75.906672856786</v>
@@ -3944,19 +3930,19 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C175" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D175" t="n">
         <v>2018</v>
       </c>
       <c r="E175" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F175" t="n">
         <v>11.5280628762572</v>
@@ -3964,19 +3950,19 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C176" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D176" t="n">
         <v>2018</v>
       </c>
       <c r="E176" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F176" t="n">
         <v>106.406106127317</v>
@@ -3984,19 +3970,19 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C177" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D177" t="n">
         <v>2018</v>
       </c>
       <c r="E177" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F177" t="n">
         <v>92.4928932177402</v>
@@ -4004,19 +3990,19 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D178" t="n">
         <v>2018</v>
       </c>
       <c r="E178" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F178" t="n">
         <v>0.106800589588266</v>
@@ -4024,19 +4010,19 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C179" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D179" t="n">
         <v>2018</v>
       </c>
       <c r="E179" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F179" t="n">
         <v>39.53707408361</v>
@@ -4044,19 +4030,19 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D180" t="n">
         <v>2018</v>
       </c>
       <c r="E180" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F180" t="n">
         <v>-143.345716957979</v>
@@ -4064,19 +4050,19 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C181" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D181" t="n">
         <v>2018</v>
       </c>
       <c r="E181" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F181" t="n">
         <v>8.55082062820805</v>
@@ -4084,19 +4070,19 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" t="s">
         <v>14</v>
-      </c>
-      <c r="B182" t="s">
-        <v>15</v>
-      </c>
-      <c r="C182" t="s">
-        <v>16</v>
       </c>
       <c r="D182" t="n">
         <v>2019</v>
       </c>
       <c r="E182" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F182" t="n">
         <v>56.7282730926873</v>
@@ -4104,19 +4090,19 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C183" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D183" t="n">
         <v>2019</v>
       </c>
       <c r="E183" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F183" t="n">
         <v>73.7678010774409</v>
@@ -4124,19 +4110,19 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D184" t="n">
         <v>2019</v>
       </c>
       <c r="E184" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F184" t="n">
         <v>11.7443620269084</v>
@@ -4144,19 +4130,19 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D185" t="n">
         <v>2019</v>
       </c>
       <c r="E185" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F185" t="n">
         <v>119.136115801918</v>
@@ -4164,19 +4150,19 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C186" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D186" t="n">
         <v>2019</v>
       </c>
       <c r="E186" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F186" t="n">
         <v>93.8736985963062</v>
@@ -4184,19 +4170,19 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D187" t="n">
         <v>2019</v>
       </c>
       <c r="E187" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F187" t="n">
         <v>0.113706182212119</v>
@@ -4204,19 +4190,19 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C188" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D188" t="n">
         <v>2019</v>
       </c>
       <c r="E188" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F188" t="n">
         <v>37.8715636232846</v>
@@ -4224,19 +4210,19 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C189" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D189" t="n">
         <v>2019</v>
       </c>
       <c r="E189" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F189" t="n">
         <v>-142.833209046815</v>
@@ -4244,19 +4230,19 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C190" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D190" t="n">
         <v>2019</v>
       </c>
       <c r="E190" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F190" t="n">
         <v>9.20369303804</v>
@@ -4264,19 +4250,19 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
+        <v>12</v>
+      </c>
+      <c r="B191" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" t="s">
         <v>14</v>
-      </c>
-      <c r="B191" t="s">
-        <v>15</v>
-      </c>
-      <c r="C191" t="s">
-        <v>16</v>
       </c>
       <c r="D191" t="n">
         <v>2020</v>
       </c>
       <c r="E191" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F191" t="n">
         <v>62.0656872352216</v>
@@ -4284,19 +4270,19 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D192" t="n">
         <v>2020</v>
       </c>
       <c r="E192" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F192" t="n">
         <v>14.4665683352222</v>
@@ -4304,19 +4290,19 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C193" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D193" t="n">
         <v>2020</v>
       </c>
       <c r="E193" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F193" t="n">
         <v>10.856456408512</v>
@@ -4324,19 +4310,19 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D194" t="n">
         <v>2020</v>
       </c>
       <c r="E194" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F194" t="n">
         <v>53.969431415238</v>
@@ -4344,19 +4330,19 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C195" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D195" t="n">
         <v>2020</v>
       </c>
       <c r="E195" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F195" t="n">
         <v>99.1577616225861</v>
@@ -4364,19 +4350,19 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C196" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D196" t="n">
         <v>2020</v>
       </c>
       <c r="E196" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F196" t="n">
         <v>76.3846372744213</v>
@@ -4384,19 +4370,19 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D197" t="n">
         <v>2020</v>
       </c>
       <c r="E197" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F197" t="n">
         <v>39.6087554879052</v>
@@ -4404,19 +4390,19 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C198" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D198" t="n">
         <v>2020</v>
       </c>
       <c r="E198" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F198" t="n">
         <v>-95.5961730938236</v>
@@ -4424,19 +4410,19 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C199" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D199" t="n">
         <v>2020</v>
       </c>
       <c r="E199" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F199" t="n">
         <v>16.3872217296375</v>
@@ -4444,19 +4430,19 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>12</v>
+      </c>
+      <c r="B200" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" t="s">
         <v>14</v>
-      </c>
-      <c r="B200" t="s">
-        <v>15</v>
-      </c>
-      <c r="C200" t="s">
-        <v>16</v>
       </c>
       <c r="D200" t="n">
         <v>2021</v>
       </c>
       <c r="E200" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F200" t="n">
         <v>66.5033109264171</v>
@@ -4464,19 +4450,19 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C201" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D201" t="n">
         <v>2021</v>
       </c>
       <c r="E201" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F201" t="n">
         <v>14.0938409304387</v>
@@ -4484,19 +4470,19 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C202" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D202" t="n">
         <v>2021</v>
       </c>
       <c r="E202" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F202" t="n">
         <v>10.3680193974429</v>
@@ -4504,19 +4490,19 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C203" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D203" t="n">
         <v>2021</v>
       </c>
       <c r="E203" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F203" t="n">
         <v>48.1288408216401</v>
@@ -4524,19 +4510,19 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C204" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D204" t="n">
         <v>2021</v>
       </c>
       <c r="E204" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F204" t="n">
         <v>98.6436750225855</v>
@@ -4544,19 +4530,19 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C205" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D205" t="n">
         <v>2021</v>
       </c>
       <c r="E205" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F205" t="n">
         <v>70.687480619284</v>
@@ -4564,19 +4550,19 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C206" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D206" t="n">
         <v>2021</v>
       </c>
       <c r="E206" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F206" t="n">
         <v>39.772808834</v>
@@ -4584,19 +4570,19 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C207" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D207" t="n">
         <v>2021</v>
       </c>
       <c r="E207" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F207" t="n">
         <v>-98.0284195296618</v>
@@ -4604,19 +4590,19 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C208" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D208" t="n">
         <v>2021</v>
       </c>
       <c r="E208" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F208" t="n">
         <v>17.588226485023</v>
@@ -4624,19 +4610,19 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
+        <v>12</v>
+      </c>
+      <c r="B209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" t="s">
         <v>14</v>
-      </c>
-      <c r="B209" t="s">
-        <v>15</v>
-      </c>
-      <c r="C209" t="s">
-        <v>16</v>
       </c>
       <c r="D209" t="n">
         <v>2022</v>
       </c>
       <c r="E209" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F209" t="n">
         <v>68.9337413993864</v>
@@ -4644,19 +4630,19 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C210" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D210" t="n">
         <v>2022</v>
       </c>
       <c r="E210" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F210" t="n">
         <v>13.990182520652</v>
@@ -4664,19 +4650,19 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C211" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D211" t="n">
         <v>2022</v>
       </c>
       <c r="E211" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F211" t="n">
         <v>8.49478401967048</v>
@@ -4684,19 +4670,19 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C212" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D212" t="n">
         <v>2022</v>
       </c>
       <c r="E212" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F212" t="n">
         <v>62.5783746337328</v>
@@ -4704,19 +4690,19 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C213" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D213" t="n">
         <v>2022</v>
       </c>
       <c r="E213" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F213" t="n">
         <v>92.2226536203189</v>
@@ -4724,19 +4710,19 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C214" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D214" t="n">
         <v>2022</v>
       </c>
       <c r="E214" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F214" t="n">
         <v>77.0213059307266</v>
@@ -4744,19 +4730,19 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C215" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D215" t="n">
         <v>2022</v>
       </c>
       <c r="E215" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F215" t="n">
         <v>40.5271186427494</v>
@@ -4764,19 +4750,19 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C216" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D216" t="n">
         <v>2022</v>
       </c>
       <c r="E216" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F216" t="n">
         <v>-107.901425467107</v>
@@ -4784,19 +4770,19 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C217" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D217" t="n">
         <v>2022</v>
       </c>
       <c r="E217" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F217" t="n">
         <v>20.5087150484657</v>

--- a/plots/countries/sectors/Thailand-sectors.xlsx
+++ b/plots/countries/sectors/Thailand-sectors.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2.1) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
